--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.348443269729614</v>
+        <v>0.02865719795227051</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999999999876464</v>
@@ -506,6 +506,41 @@
         <v>5.051934608765776e-05</v>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.03991985321044922</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.999999999988234</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.99999999998775</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.89727434653534e-05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.051934608765776e-05</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
         </is>
@@ -522,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.348443269729614</v>
+        <v>0.02865719795227051</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999999999876464</v>
@@ -602,6 +637,41 @@
         <v>5.051934608765776e-05</v>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.03991985321044922</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.999999999988234</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.99999999998775</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.89727434653534e-05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.051934608765776e-05</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
         </is>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02865719795227051</v>
+        <v>0.03978371620178223</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999999999876464</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03991985321044922</v>
+        <v>0.03991532325744629</v>
       </c>
       <c r="E3" t="n">
         <v>0.999999999988234</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02865719795227051</v>
+        <v>0.03978371620178223</v>
       </c>
       <c r="E2" t="n">
         <v>0.9999999999876464</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03991985321044922</v>
+        <v>0.03991532325744629</v>
       </c>
       <c r="E3" t="n">
         <v>0.999999999988234</v>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03978371620178223</v>
+        <v>0.06342554092407227</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999999876464</v>
+        <v>0.9095325244128653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.99999999998775</v>
+        <v>0.9134070331993437</v>
       </c>
       <c r="G2" t="n">
-        <v>6.89727434653534e-05</v>
+        <v>5.798964155976802</v>
       </c>
       <c r="H2" t="n">
-        <v>5.051934608765776e-05</v>
+        <v>4.192993498939789</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03991532325744629</v>
+        <v>0.08275389671325684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.999999999988234</v>
+        <v>0.9087532778197251</v>
       </c>
       <c r="F3" t="n">
-        <v>0.99999999998775</v>
+        <v>0.9134070331993437</v>
       </c>
       <c r="G3" t="n">
-        <v>6.89727434653534e-05</v>
+        <v>5.798964155976802</v>
       </c>
       <c r="H3" t="n">
-        <v>5.051934608765776e-05</v>
+        <v>4.192993498939789</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03978371620178223</v>
+        <v>0.06342554092407227</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999999999876464</v>
+        <v>0.9095325244128653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.99999999998775</v>
+        <v>0.9134070331993437</v>
       </c>
       <c r="G2" t="n">
-        <v>6.89727434653534e-05</v>
+        <v>5.798964155976802</v>
       </c>
       <c r="H2" t="n">
-        <v>5.051934608765776e-05</v>
+        <v>4.192993498939789</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03991532325744629</v>
+        <v>0.08275389671325684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.999999999988234</v>
+        <v>0.9087532778197251</v>
       </c>
       <c r="F3" t="n">
-        <v>0.99999999998775</v>
+        <v>0.9134070331993437</v>
       </c>
       <c r="G3" t="n">
-        <v>6.89727434653534e-05</v>
+        <v>5.798964155976802</v>
       </c>
       <c r="H3" t="n">
-        <v>5.051934608765776e-05</v>
+        <v>4.192993498939789</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06342554092407227</v>
+        <v>9.293736219406128</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.3876247645046073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.3881716909782678</v>
       </c>
       <c r="G2" t="n">
-        <v>5.798964155976802</v>
+        <v>139.1897807759676</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192993498939789</v>
+        <v>104.7955168833389</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08275389671325684</v>
+        <v>9.57185173034668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087532778197251</v>
+        <v>0.3875160662916951</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.3881716909782678</v>
       </c>
       <c r="G3" t="n">
-        <v>5.798964155976802</v>
+        <v>139.1897807759676</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192993498939789</v>
+        <v>104.7955168833389</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10.36987042427063</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3874155138996928</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3881716909782678</v>
+      </c>
+      <c r="G4" t="n">
+        <v>139.1897807759676</v>
+      </c>
+      <c r="H4" t="n">
+        <v>104.7955168833389</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06342554092407227</v>
+        <v>9.293736219406128</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095325244128653</v>
+        <v>0.3876247645046073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.3881716909782678</v>
       </c>
       <c r="G2" t="n">
-        <v>5.798964155976802</v>
+        <v>139.1897807759676</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192993498939789</v>
+        <v>104.7955168833389</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08275389671325684</v>
+        <v>9.57185173034668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087532778197251</v>
+        <v>0.3875160662916951</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9134070331993437</v>
+        <v>0.3881716909782678</v>
       </c>
       <c r="G3" t="n">
-        <v>5.798964155976802</v>
+        <v>139.1897807759676</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192993498939789</v>
+        <v>104.7955168833389</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'random'}</t>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10.36987042427063</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3874155138996928</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3881716909782678</v>
+      </c>
+      <c r="G4" t="n">
+        <v>139.1897807759676</v>
+      </c>
+      <c r="H4" t="n">
+        <v>104.7955168833389</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.293736219406128</v>
+        <v>0.1129672527313232</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3876247645046073</v>
+        <v>0.9095174369097344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3881716909782678</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1897807759676</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7955168833389</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.57185173034668</v>
+        <v>0.0507209300994873</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875160662916951</v>
+        <v>0.9087447139966063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3881716909782678</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1897807759676</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7955168833389</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10.36987042427063</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3874155138996928</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3881716909782678</v>
-      </c>
-      <c r="G4" t="n">
-        <v>139.1897807759676</v>
-      </c>
-      <c r="H4" t="n">
-        <v>104.7955168833389</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.293736219406128</v>
+        <v>0.1129672527313232</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3876247645046073</v>
+        <v>0.9095174369097344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3881716909782678</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1897807759676</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7955168833389</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9.57185173034668</v>
+        <v>0.0507209300994873</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875160662916951</v>
+        <v>0.9087447139966063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3881716909782678</v>
+        <v>0.9133112678275858</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1897807759676</v>
+        <v>5.802169881120578</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7955168833389</v>
+        <v>4.19427635989441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10.36987042427063</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3874155138996928</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3881716909782678</v>
-      </c>
-      <c r="G4" t="n">
-        <v>139.1897807759676</v>
-      </c>
-      <c r="H4" t="n">
-        <v>104.7955168833389</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'alpha': 1e-05, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1129672527313232</v>
+        <v>0.04944562911987305</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095174369097344</v>
+        <v>0.9095307134779663</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133112678275858</v>
+        <v>0.9133998765984722</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802169881120578</v>
+        <v>5.799203782912025</v>
       </c>
       <c r="H2" t="n">
-        <v>4.19427635989441</v>
+        <v>4.192790055171488</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.0001, 'max_iter': 10000, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0507209300994873</v>
+        <v>0.06251907348632812</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087447139966063</v>
+        <v>0.9087514890888293</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133112678275858</v>
+        <v>0.9133998765984722</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802169881120578</v>
+        <v>5.799203782912025</v>
       </c>
       <c r="H3" t="n">
-        <v>4.19427635989441</v>
+        <v>4.192790055171488</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.0001, 'max_iter': 10000, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1129672527313232</v>
+        <v>0.04944562911987305</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095174369097344</v>
+        <v>0.9095307134779663</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133112678275858</v>
+        <v>0.9133998765984722</v>
       </c>
       <c r="G2" t="n">
-        <v>5.802169881120578</v>
+        <v>5.799203782912025</v>
       </c>
       <c r="H2" t="n">
-        <v>4.19427635989441</v>
+        <v>4.192790055171488</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.0001, 'max_iter': 10000, 'selection': 'random'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0507209300994873</v>
+        <v>0.06251907348632812</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087447139966063</v>
+        <v>0.9087514890888293</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133112678275858</v>
+        <v>0.9133998765984722</v>
       </c>
       <c r="G3" t="n">
-        <v>5.802169881120578</v>
+        <v>5.799203782912025</v>
       </c>
       <c r="H3" t="n">
-        <v>4.19427635989441</v>
+        <v>4.192790055171488</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'selection': 'cyclic'}</t>
+          <t>{'alpha': 0.0001, 'max_iter': 10000, 'selection': 'random'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04944562911987305</v>
+        <v>0.08975768089294434</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095307134779663</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133998765984722</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799203782912025</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192790055171488</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'max_iter': 10000, 'selection': 'random'}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06251907348632812</v>
+        <v>0.04338216781616211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087514890888293</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133998765984722</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799203782912025</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192790055171488</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'max_iter': 10000, 'selection': 'random'}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04944562911987305</v>
+        <v>0.08975768089294434</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095307134779663</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133998765984722</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799203782912025</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192790055171488</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'max_iter': 10000, 'selection': 'random'}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06251907348632812</v>
+        <v>0.04338216781616211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087514890888293</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133998765984722</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799203782912025</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192790055171488</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.0001, 'max_iter': 10000, 'selection': 'random'}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08975768089294434</v>
+        <v>0.0304255485534668</v>
       </c>
       <c r="E2" t="n">
         <v>0.9095314697018355</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04338216781616211</v>
+        <v>0.05216598510742188</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087547686315594</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08975768089294434</v>
+        <v>0.0304255485534668</v>
       </c>
       <c r="E2" t="n">
         <v>0.9095314697018355</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04338216781616211</v>
+        <v>0.05216598510742188</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087547686315594</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0304255485534668</v>
+        <v>79.96605229377747</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095314697018355</v>
+        <v>0.387644777846075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133925467063826</v>
+        <v>0.3881966456514309</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799449201953228</v>
+        <v>139.1869421765973</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192818052928173</v>
+        <v>104.7894206132718</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05216598510742188</v>
+        <v>63.57240629196167</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087547686315594</v>
+        <v>0.3875372233114082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133935968581072</v>
+        <v>0.3881966456514309</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799414041468699</v>
+        <v>139.1869421765973</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192899764404125</v>
+        <v>104.7894206132718</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0304255485534668</v>
+        <v>79.96605229377747</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095314697018355</v>
+        <v>0.387644777846075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133925467063826</v>
+        <v>0.3881966456514309</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799449201953228</v>
+        <v>139.1869421765973</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192818052928173</v>
+        <v>104.7894206132718</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05216598510742188</v>
+        <v>63.57240629196167</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087547686315594</v>
+        <v>0.3875372233114082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133935968581072</v>
+        <v>0.3881966456514309</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799414041468699</v>
+        <v>139.1869421765973</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192899764404125</v>
+        <v>104.7894206132718</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>79.96605229377747</v>
+        <v>0.0574958324432373</v>
       </c>
       <c r="E2" t="n">
-        <v>0.387644777846075</v>
+        <v>0.2762198267065196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.2642087227138233</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1869421765973</v>
+        <v>0.7548844799725748</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7894206132718</v>
+        <v>0.5870174989191963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>63.57240629196167</v>
+        <v>0.06962919235229492</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875372233114082</v>
+        <v>0.2776218701339047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.2642022548184634</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1869421765973</v>
+        <v>0.7548877978313523</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7894206132718</v>
+        <v>0.5870198778151539</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>79.96605229377747</v>
+        <v>0.0574958324432373</v>
       </c>
       <c r="E2" t="n">
-        <v>0.387644777846075</v>
+        <v>0.2762198267065196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.2642087227138233</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1869421765973</v>
+        <v>0.7548844799725748</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7894206132718</v>
+        <v>0.5870174989191963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>63.57240629196167</v>
+        <v>0.06962919235229492</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875372233114082</v>
+        <v>0.2776218701339047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.2642022548184634</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1869421765973</v>
+        <v>0.7548877978313523</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7894206132718</v>
+        <v>0.5870198778151539</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0574958324432373</v>
+        <v>5.72333025932312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2762198267065196</v>
+        <v>0.1631297501254156</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2642087227138233</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7548844799725748</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5870174989191963</v>
+        <v>52.59974169016452</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06962919235229492</v>
+        <v>6.8518967628479</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2776218701339047</v>
+        <v>0.1637257443267972</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2642022548184634</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7548877978313523</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5870198778151539</v>
+        <v>52.59974169016452</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0574958324432373</v>
+        <v>5.72333025932312</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2762198267065196</v>
+        <v>0.1631297501254156</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2642087227138233</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7548844799725748</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5870174989191963</v>
+        <v>52.59974169016452</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06962919235229492</v>
+        <v>6.8518967628479</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2776218701339047</v>
+        <v>0.1637257443267972</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2642022548184634</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7548877978313523</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5870198778151539</v>
+        <v>52.59974169016452</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.72333025932312</v>
+        <v>0.04096603393554688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631297501254156</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.168803458291798</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G2" t="n">
-        <v>91.20229991586648</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59974169016452</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8518967628479</v>
+        <v>0.05547475814819336</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637257443267972</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.168803458291798</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G3" t="n">
-        <v>91.20229991586648</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H3" t="n">
-        <v>52.59974169016452</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08036041259765625</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090587832930842</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.913146287430656</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.807688414253744</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197174702000158</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.72333025932312</v>
+        <v>0.04096603393554688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631297501254156</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.168803458291798</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G2" t="n">
-        <v>91.20229991586648</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59974169016452</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8518967628479</v>
+        <v>0.05547475814819336</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637257443267972</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.168803458291798</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G3" t="n">
-        <v>91.20229991586648</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H3" t="n">
-        <v>52.59974169016452</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08036041259765625</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090587832930842</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.913146287430656</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.807688414253744</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197174702000158</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04096603393554688</v>
+        <v>35.90342903137207</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095314697018355</v>
+        <v>0.387644777846075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133925467063826</v>
+        <v>0.3881966456514309</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799449201953228</v>
+        <v>139.1869421765973</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192818052928173</v>
+        <v>104.7894206132718</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05547475814819336</v>
+        <v>37.20738410949707</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087547686315594</v>
+        <v>0.3875372233114082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133935968581072</v>
+        <v>0.3881966456514309</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799414041468699</v>
+        <v>139.1869421765973</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192899764404125</v>
+        <v>104.7894206132718</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.08036041259765625</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090587832930842</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.913146287430656</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.807688414253744</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197174702000158</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04096603393554688</v>
+        <v>35.90342903137207</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095314697018355</v>
+        <v>0.387644777846075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133925467063826</v>
+        <v>0.3881966456514309</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799449201953228</v>
+        <v>139.1869421765973</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192818052928173</v>
+        <v>104.7894206132718</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05547475814819336</v>
+        <v>37.20738410949707</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087547686315594</v>
+        <v>0.3875372233114082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133935968581072</v>
+        <v>0.3881966456514309</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799414041468699</v>
+        <v>139.1869421765973</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192899764404125</v>
+        <v>104.7894206132718</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.08036041259765625</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090587832930842</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.913146287430656</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.807688414253744</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197174702000158</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>35.90342903137207</v>
+        <v>0.2415382862091064</v>
       </c>
       <c r="E2" t="n">
-        <v>0.387644777846075</v>
+        <v>0.9900982229669099</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.9902541220814914</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1869421765973</v>
+        <v>0.9477199190161582</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7894206132718</v>
+        <v>0.7418471020336928</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>37.20738410949707</v>
+        <v>0.3280642032623291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875372233114082</v>
+        <v>0.9900985706256581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.9902541076781655</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1869421765973</v>
+        <v>0.9477206193283345</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7894206132718</v>
+        <v>0.7418330359163595</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>35.90342903137207</v>
+        <v>0.2415382862091064</v>
       </c>
       <c r="E2" t="n">
-        <v>0.387644777846075</v>
+        <v>0.9900982229669099</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.9902541220814914</v>
       </c>
       <c r="G2" t="n">
-        <v>139.1869421765973</v>
+        <v>0.9477199190161582</v>
       </c>
       <c r="H2" t="n">
-        <v>104.7894206132718</v>
+        <v>0.7418471020336928</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>37.20738410949707</v>
+        <v>0.3280642032623291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3875372233114082</v>
+        <v>0.9900985706256581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3881966456514309</v>
+        <v>0.9902541076781655</v>
       </c>
       <c r="G3" t="n">
-        <v>139.1869421765973</v>
+        <v>0.9477206193283345</v>
       </c>
       <c r="H3" t="n">
-        <v>104.7894206132718</v>
+        <v>0.7418330359163595</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2415382862091064</v>
+        <v>5.73303747177124</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9900982229669099</v>
+        <v>0.1631297501254156</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9902541220814914</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9477199190161582</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7418471020336928</v>
+        <v>52.59974169016452</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3280642032623291</v>
+        <v>6.808621406555176</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9900985706256581</v>
+        <v>0.1637257443267972</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9902541076781655</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9477206193283345</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7418330359163595</v>
+        <v>52.59974169016452</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2415382862091064</v>
+        <v>5.73303747177124</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9900982229669099</v>
+        <v>0.1631297501254156</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9902541220814914</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9477199190161582</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7418471020336928</v>
+        <v>52.59974169016452</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3280642032623291</v>
+        <v>6.808621406555176</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9900985706256581</v>
+        <v>0.1637257443267972</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9902541076781655</v>
+        <v>0.168803458291798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9477206193283345</v>
+        <v>91.20229991586648</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7418330359163595</v>
+        <v>52.59974169016452</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.73303747177124</v>
+        <v>183.1296489238739</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631297501254156</v>
+        <v>0.7337649931248545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.168803458291798</v>
+        <v>0.7371529686246404</v>
       </c>
       <c r="G2" t="n">
-        <v>91.20229991586648</v>
+        <v>17.39419673883764</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59974169016452</v>
+        <v>13.20418315547962</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.808621406555176</v>
+        <v>206.5332767963409</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637257443267972</v>
+        <v>0.7338476286732339</v>
       </c>
       <c r="F3" t="n">
-        <v>0.168803458291798</v>
+        <v>0.7371529686246404</v>
       </c>
       <c r="G3" t="n">
-        <v>91.20229991586648</v>
+        <v>17.39419673883764</v>
       </c>
       <c r="H3" t="n">
-        <v>52.59974169016452</v>
+        <v>13.20418315547962</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.73303747177124</v>
+        <v>183.1296489238739</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1631297501254156</v>
+        <v>0.7337649931248545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.168803458291798</v>
+        <v>0.7371529686246404</v>
       </c>
       <c r="G2" t="n">
-        <v>91.20229991586648</v>
+        <v>17.39419673883764</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59974169016452</v>
+        <v>13.20418315547962</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.808621406555176</v>
+        <v>206.5332767963409</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1637257443267972</v>
+        <v>0.7338476286732339</v>
       </c>
       <c r="F3" t="n">
-        <v>0.168803458291798</v>
+        <v>0.7371529686246404</v>
       </c>
       <c r="G3" t="n">
-        <v>91.20229991586648</v>
+        <v>17.39419673883764</v>
       </c>
       <c r="H3" t="n">
-        <v>52.59974169016452</v>
+        <v>13.20418315547962</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>183.1296489238739</v>
+        <v>0.03827381134033203</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7337649931248545</v>
+        <v>0.2762198267065196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7371529686246404</v>
+        <v>0.2642087227138233</v>
       </c>
       <c r="G2" t="n">
-        <v>17.39419673883764</v>
+        <v>0.7548844799725748</v>
       </c>
       <c r="H2" t="n">
-        <v>13.20418315547962</v>
+        <v>0.5870174989191963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>206.5332767963409</v>
+        <v>0.1115138530731201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7338476286732339</v>
+        <v>0.2776218701339047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7371529686246404</v>
+        <v>0.2642022548184634</v>
       </c>
       <c r="G3" t="n">
-        <v>17.39419673883764</v>
+        <v>0.7548877978313523</v>
       </c>
       <c r="H3" t="n">
-        <v>13.20418315547962</v>
+        <v>0.5870198778151539</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>183.1296489238739</v>
+        <v>0.03827381134033203</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7337649931248545</v>
+        <v>0.2762198267065196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7371529686246404</v>
+        <v>0.2642087227138233</v>
       </c>
       <c r="G2" t="n">
-        <v>17.39419673883764</v>
+        <v>0.7548844799725748</v>
       </c>
       <c r="H2" t="n">
-        <v>13.20418315547962</v>
+        <v>0.5870174989191963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>206.5332767963409</v>
+        <v>0.1115138530731201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7338476286732339</v>
+        <v>0.2776218701339047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7371529686246404</v>
+        <v>0.2642022548184634</v>
       </c>
       <c r="G3" t="n">
-        <v>17.39419673883764</v>
+        <v>0.7548877978313523</v>
       </c>
       <c r="H3" t="n">
-        <v>13.20418315547962</v>
+        <v>0.5870198778151539</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03827381134033203</v>
+        <v>0.04252243041992188</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2762198267065196</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2642087227138233</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7548844799725748</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5870174989191963</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1115138530731201</v>
+        <v>0.0679774284362793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2776218701339047</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2642022548184634</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7548877978313523</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5870198778151539</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09312987327575684</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090587832930842</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.913146287430656</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.807688414253744</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197174702000158</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03827381134033203</v>
+        <v>0.04252243041992188</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2762198267065196</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2642087227138233</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7548844799725748</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5870174989191963</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'cyclic', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1115138530731201</v>
+        <v>0.0679774284362793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2776218701339047</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2642022548184634</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7548877978313523</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5870198778151539</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'alpha': 0.001, 'max_iter': 10000, 'selection': 'random', 'tol': 0.0001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09312987327575684</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090587832930842</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.913146287430656</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.807688414253744</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197174702000158</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04252243041992188</v>
+        <v>0.04329729080200195</v>
       </c>
       <c r="E2" t="n">
         <v>0.9095314697018355</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0679774284362793</v>
+        <v>0.1056342124938965</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087547686315594</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09312987327575684</v>
+        <v>0.1326797008514404</v>
       </c>
       <c r="E4" t="n">
         <v>0.9090587832930842</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04252243041992188</v>
+        <v>0.04329729080200195</v>
       </c>
       <c r="E2" t="n">
         <v>0.9095314697018355</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0679774284362793</v>
+        <v>0.1056342124938965</v>
       </c>
       <c r="E3" t="n">
         <v>0.9087547686315594</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09312987327575684</v>
+        <v>0.1326797008514404</v>
       </c>
       <c r="E4" t="n">
         <v>0.9090587832930842</v>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04329729080200195</v>
+        <v>0.6050491333007812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095314697018355</v>
+        <v>0.3879948745862398</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133925467063826</v>
+        <v>0.3786827871069254</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799449201953228</v>
+        <v>105.1272696664699</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192818052928173</v>
+        <v>79.44687800082798</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1056342124938965</v>
+        <v>0.7991194725036621</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087547686315594</v>
+        <v>0.3876229557024191</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133935968581072</v>
+        <v>0.3786827871069254</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799414041468699</v>
+        <v>105.1272696664699</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192899764404125</v>
+        <v>79.44687800082798</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1326797008514404</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090587832930842</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.913146287430656</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.807688414253744</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197174702000158</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04329729080200195</v>
+        <v>0.6050491333007812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9095314697018355</v>
+        <v>0.3879948745862398</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9133925467063826</v>
+        <v>0.3786827871069254</v>
       </c>
       <c r="G2" t="n">
-        <v>5.799449201953228</v>
+        <v>105.1272696664699</v>
       </c>
       <c r="H2" t="n">
-        <v>4.192818052928173</v>
+        <v>79.44687800082798</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1056342124938965</v>
+        <v>0.7991194725036621</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9087547686315594</v>
+        <v>0.3876229557024191</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9133935968581072</v>
+        <v>0.3786827871069254</v>
       </c>
       <c r="G3" t="n">
-        <v>5.799414041468699</v>
+        <v>105.1272696664699</v>
       </c>
       <c r="H3" t="n">
-        <v>4.192899764404125</v>
+        <v>79.44687800082798</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1326797008514404</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9090587832930842</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.913146287430656</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.807688414253744</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.197174702000158</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_Lasso_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6050491333007812</v>
+        <v>0.1089096069335938</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3879948745862398</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3786827871069254</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G2" t="n">
-        <v>105.1272696664699</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H2" t="n">
-        <v>79.44687800082798</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7991194725036621</v>
+        <v>0.0565636157989502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876229557024191</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3786827871069254</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G3" t="n">
-        <v>105.1272696664699</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H3" t="n">
-        <v>79.44687800082798</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09963870048522949</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090587832930842</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.913146287430656</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.807688414253744</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197174702000158</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6050491333007812</v>
+        <v>0.1089096069335938</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3879948745862398</v>
+        <v>0.9095314697018355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3786827871069254</v>
+        <v>0.9133925467063826</v>
       </c>
       <c r="G2" t="n">
-        <v>105.1272696664699</v>
+        <v>5.799449201953228</v>
       </c>
       <c r="H2" t="n">
-        <v>79.44687800082798</v>
+        <v>4.192818052928173</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'cyclic', 'max_iter': 10000, 'alpha': 0.001}</t>
         </is>
       </c>
     </row>
@@ -654,26 +689,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7991194725036621</v>
+        <v>0.0565636157989502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3876229557024191</v>
+        <v>0.9087547686315594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3786827871069254</v>
+        <v>0.9133935968581072</v>
       </c>
       <c r="G3" t="n">
-        <v>105.1272696664699</v>
+        <v>5.799414041468699</v>
       </c>
       <c r="H3" t="n">
-        <v>79.44687800082798</v>
+        <v>4.192899764404125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.1}</t>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.001}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09963870048522949</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9090587832930842</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.913146287430656</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.807688414253744</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.197174702000158</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'tol': 0.0001, 'selection': 'random', 'max_iter': 10000, 'alpha': 0.01}</t>
         </is>
       </c>
     </row>
